--- a/erp-server/erp-server-file/src/main/resources/excel/wms/poReturnExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/poReturnExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
   <si>
     <t>退货单号</t>
   </si>
@@ -35,6 +35,12 @@
     <t>采购单号</t>
   </si>
   <si>
+    <t>委外订单</t>
+  </si>
+  <si>
+    <t>退货类型</t>
+  </si>
+  <si>
     <t>供应商</t>
   </si>
   <si>
@@ -107,6 +113,12 @@
     <t>{.purchaseOrderCode}</t>
   </si>
   <si>
+    <t>{.purchaseSourceCode}</t>
+  </si>
+  <si>
+    <t>{.returnModeName}</t>
+  </si>
+  <si>
     <t>{.supplierName}</t>
   </si>
   <si>
@@ -141,9 +153,6 @@
   </si>
   <si>
     <t>{.returnRemark}</t>
-  </si>
-  <si>
-    <t>{.returnModeName}</t>
   </si>
   <si>
     <t>{.purchaseUserName}</t>
@@ -208,17 +217,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -852,10 +861,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1209,35 +1218,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
-    <col min="2" max="2" width="14.75" customWidth="1"/>
-    <col min="3" max="3" width="29.5" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="8.75" customWidth="1"/>
-    <col min="6" max="6" width="7.375" customWidth="1"/>
-    <col min="7" max="7" width="12.75" customWidth="1"/>
-    <col min="8" max="8" width="28.75" customWidth="1"/>
-    <col min="9" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="16.125" customWidth="1"/>
-    <col min="12" max="12" width="23.375" customWidth="1"/>
-    <col min="13" max="13" width="9.25" customWidth="1"/>
-    <col min="14" max="14" width="22.125" customWidth="1"/>
-    <col min="15" max="15" width="12.125" customWidth="1"/>
-    <col min="16" max="16" width="8" customWidth="1"/>
-    <col min="17" max="17" width="7.875" customWidth="1"/>
-    <col min="18" max="18" width="19.75" customWidth="1"/>
-    <col min="19" max="19" width="10.625" customWidth="1"/>
-    <col min="20" max="20" width="23.625" customWidth="1"/>
-    <col min="22" max="22" width="9.625" customWidth="1"/>
-    <col min="23" max="23" width="8.25" customWidth="1"/>
-    <col min="24" max="24" width="22.125" customWidth="1"/>
-    <col min="25" max="25" width="18" customWidth="1"/>
+    <col min="2" max="4" width="14.75" customWidth="1"/>
+    <col min="5" max="5" width="29.5" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="8.75" customWidth="1"/>
+    <col min="8" max="8" width="7.375" customWidth="1"/>
+    <col min="9" max="9" width="12.75" customWidth="1"/>
+    <col min="10" max="10" width="28.75" customWidth="1"/>
+    <col min="11" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="23.375" customWidth="1"/>
+    <col min="15" max="15" width="9.25" customWidth="1"/>
+    <col min="16" max="16" width="22.125" customWidth="1"/>
+    <col min="17" max="17" width="12.125" customWidth="1"/>
+    <col min="18" max="18" width="8" customWidth="1"/>
+    <col min="19" max="19" width="7.875" customWidth="1"/>
+    <col min="20" max="20" width="19.75" customWidth="1"/>
+    <col min="21" max="21" width="10.625" customWidth="1"/>
+    <col min="22" max="22" width="23.625" customWidth="1"/>
+    <col min="24" max="24" width="9.625" customWidth="1"/>
+    <col min="25" max="25" width="8.25" customWidth="1"/>
+    <col min="26" max="26" width="22.125" customWidth="1"/>
+    <col min="27" max="27" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:24">
+    <row r="1" s="1" customFormat="1" spans="1:26">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1259,13 +1268,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
@@ -1277,10 +1286,10 @@
       <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="2" t="s">
@@ -1298,91 +1307,103 @@
       <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="4" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
-      <c r="A2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" s="4" t="s">
+    <row r="2" spans="1:26">
+      <c r="A2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="N2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="O2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="R2" s="4" t="s">
+      <c r="P2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="Q2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="T2" s="4" t="s">
+      <c r="S2" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="U2" s="4" t="s">
+      <c r="T2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="V2" s="4" t="s">
+      <c r="U2" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="W2" s="4" t="s">
+      <c r="V2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="X2" s="4" t="s">
+      <c r="W2" s="3" t="s">
         <v>47</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/poReturnExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/poReturnExport.xlsx
@@ -113,7 +113,7 @@
     <t>{.purchaseOrderCode}</t>
   </si>
   <si>
-    <t>{.purchaseSourceCode}</t>
+    <t>{.subcontractCode}</t>
   </si>
   <si>
     <t>{.returnModeName}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/poReturnExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/poReturnExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="65">
   <si>
     <t>退货单号</t>
   </si>
@@ -68,12 +68,30 @@
     <t>退货确认日期</t>
   </si>
   <si>
+    <t>采购组织</t>
+  </si>
+  <si>
+    <t>退货组织</t>
+  </si>
+  <si>
     <t>仓库</t>
   </si>
   <si>
+    <t>仓位</t>
+  </si>
+  <si>
     <t>退货数量</t>
   </si>
   <si>
+    <t>补货数量</t>
+  </si>
+  <si>
+    <t>扣款数量</t>
+  </si>
+  <si>
+    <t>退货来源</t>
+  </si>
+  <si>
     <t>退货原因</t>
   </si>
   <si>
@@ -101,6 +119,9 @@
     <t>审核人(最新)</t>
   </si>
   <si>
+    <t>审核完成时间</t>
+  </si>
+  <si>
     <t>创建人</t>
   </si>
   <si>
@@ -146,12 +167,30 @@
     <t>{.confirmDate}</t>
   </si>
   <si>
+    <t>{.purchaseOrgName}</t>
+  </si>
+  <si>
+    <t>{.returnOrgName}</t>
+  </si>
+  <si>
     <t>{.returnWarehouseName}</t>
   </si>
   <si>
+    <t>{.warehouseLocationName}</t>
+  </si>
+  <si>
     <t>{.returnQty}</t>
   </si>
   <si>
+    <t>{.replenishQty}</t>
+  </si>
+  <si>
+    <t>{.deductAmountQty}</t>
+  </si>
+  <si>
+    <t>{.returnOrderSourceName}</t>
+  </si>
+  <si>
     <t>{.returnRemark}</t>
   </si>
   <si>
@@ -174,6 +213,9 @@
   </si>
   <si>
     <t>{.approveUserName}</t>
+  </si>
+  <si>
+    <t>{.approveTime}</t>
   </si>
   <si>
     <t>{.createUserName}</t>
@@ -1218,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1231,22 +1273,26 @@
     <col min="10" max="10" width="28.75" customWidth="1"/>
     <col min="11" max="12" width="13" customWidth="1"/>
     <col min="13" max="13" width="16.125" customWidth="1"/>
-    <col min="14" max="14" width="23.375" customWidth="1"/>
-    <col min="15" max="15" width="9.25" customWidth="1"/>
-    <col min="16" max="16" width="22.125" customWidth="1"/>
-    <col min="17" max="17" width="12.125" customWidth="1"/>
-    <col min="18" max="18" width="8" customWidth="1"/>
-    <col min="19" max="19" width="7.875" customWidth="1"/>
-    <col min="20" max="20" width="19.75" customWidth="1"/>
-    <col min="21" max="21" width="10.625" customWidth="1"/>
-    <col min="22" max="22" width="23.625" customWidth="1"/>
-    <col min="24" max="24" width="9.625" customWidth="1"/>
-    <col min="25" max="25" width="8.25" customWidth="1"/>
-    <col min="26" max="26" width="22.125" customWidth="1"/>
-    <col min="27" max="27" width="18" customWidth="1"/>
+    <col min="14" max="17" width="23.375" customWidth="1"/>
+    <col min="18" max="18" width="9.25" customWidth="1"/>
+    <col min="19" max="19" width="10" customWidth="1"/>
+    <col min="20" max="20" width="9.25" customWidth="1"/>
+    <col min="21" max="21" width="12.25" customWidth="1"/>
+    <col min="22" max="22" width="22.125" customWidth="1"/>
+    <col min="23" max="23" width="12.125" customWidth="1"/>
+    <col min="24" max="24" width="8" customWidth="1"/>
+    <col min="25" max="25" width="7.875" customWidth="1"/>
+    <col min="26" max="26" width="19.75" customWidth="1"/>
+    <col min="27" max="27" width="10.625" customWidth="1"/>
+    <col min="28" max="28" width="23.625" customWidth="1"/>
+    <col min="30" max="30" width="9.625" customWidth="1"/>
+    <col min="31" max="31" width="22.125" customWidth="1"/>
+    <col min="32" max="32" width="8.25" customWidth="1"/>
+    <col min="33" max="33" width="22.125" customWidth="1"/>
+    <col min="34" max="34" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:26">
+    <row r="1" s="1" customFormat="1" spans="1:33">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1292,28 +1338,28 @@
       <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="2" t="s">
@@ -1325,85 +1371,127 @@
       <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:33">
       <c r="A2" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="W2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="X2" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/poReturnExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/poReturnExport.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24945" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
   <si>
     <t>退货单号</t>
   </si>
@@ -83,6 +83,12 @@
     <t>退货数量</t>
   </si>
   <si>
+    <t>退款单价</t>
+  </si>
+  <si>
+    <t>退款总额</t>
+  </si>
+  <si>
     <t>补货数量</t>
   </si>
   <si>
@@ -180,6 +186,12 @@
   </si>
   <si>
     <t>{.returnQty}</t>
+  </si>
+  <si>
+    <t>{.returnPrice}</t>
+  </si>
+  <si>
+    <t>{.deductAmountAmount}</t>
   </si>
   <si>
     <t>{.replenishQty}</t>
@@ -1260,7 +1272,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1275,24 +1287,25 @@
     <col min="13" max="13" width="16.125" customWidth="1"/>
     <col min="14" max="17" width="23.375" customWidth="1"/>
     <col min="18" max="18" width="9.25" customWidth="1"/>
-    <col min="19" max="19" width="10" customWidth="1"/>
-    <col min="20" max="20" width="9.25" customWidth="1"/>
-    <col min="21" max="21" width="12.25" customWidth="1"/>
-    <col min="22" max="22" width="22.125" customWidth="1"/>
-    <col min="23" max="23" width="12.125" customWidth="1"/>
-    <col min="24" max="24" width="8" customWidth="1"/>
-    <col min="25" max="25" width="7.875" customWidth="1"/>
-    <col min="26" max="26" width="19.75" customWidth="1"/>
-    <col min="27" max="27" width="10.625" customWidth="1"/>
-    <col min="28" max="28" width="23.625" customWidth="1"/>
-    <col min="30" max="30" width="9.625" customWidth="1"/>
-    <col min="31" max="31" width="22.125" customWidth="1"/>
-    <col min="32" max="32" width="8.25" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="20" max="21" width="10" customWidth="1"/>
+    <col min="22" max="22" width="9.25" customWidth="1"/>
+    <col min="23" max="23" width="12.25" customWidth="1"/>
+    <col min="24" max="24" width="22.125" customWidth="1"/>
+    <col min="25" max="25" width="12.125" customWidth="1"/>
+    <col min="26" max="26" width="8" customWidth="1"/>
+    <col min="27" max="27" width="7.875" customWidth="1"/>
+    <col min="28" max="28" width="19.75" customWidth="1"/>
+    <col min="29" max="29" width="10.625" customWidth="1"/>
+    <col min="30" max="30" width="23.625" customWidth="1"/>
+    <col min="32" max="32" width="9.625" customWidth="1"/>
     <col min="33" max="33" width="22.125" customWidth="1"/>
-    <col min="34" max="34" width="18" customWidth="1"/>
+    <col min="34" max="34" width="8.25" customWidth="1"/>
+    <col min="35" max="35" width="22.125" customWidth="1"/>
+    <col min="36" max="36" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:33">
+    <row r="1" s="1" customFormat="1" spans="1:35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1356,10 +1369,10 @@
       <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="2" t="s">
@@ -1377,13 +1390,13 @@
       <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
       <c r="AF1" s="2" t="s">
@@ -1392,106 +1405,118 @@
       <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="AH1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:35">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y2" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y2" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="Z2" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
